--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/VIRGINIA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/VIRGINIA_2024.xlsx
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C217">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C477">
